--- a/data/raw/sales/Week 24/Tonor/amazon_sales.xlsx
+++ b/data/raw/sales/Week 24/Tonor/amazon_sales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Week 17\Week 24\raw\sales\Week 24\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 24\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E02E9B-FDE0-46D4-8E66-EC72952B50AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1BF1ED-5336-4897-9A06-2E1F8A0A67CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
   <si>
     <t>(Parent) ASIN</t>
   </si>
@@ -235,306 +235,15 @@
   </si>
   <si>
     <t>TONOR TM310 USB Conference Microphone for Laptop, Adjustable Computer PC Mic with Mute Button &amp; LED Indicator for Video Call Meeting, Mic for Desktop Zoom Skype YouTube, Plug-Play for MacOS Windows</t>
-  </si>
-  <si>
-    <t>470</t>
-  </si>
-  <si>
-    <t>0.41%</t>
-  </si>
-  <si>
-    <t>0.39%</t>
-  </si>
-  <si>
-    <t>636</t>
-  </si>
-  <si>
-    <t>0.43%</t>
-  </si>
-  <si>
-    <t>0.47%</t>
-  </si>
-  <si>
-    <t>1.03%</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>0.21%</t>
-  </si>
-  <si>
-    <t>₹0.00</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>0.06%</t>
-  </si>
-  <si>
-    <t>0.13%</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>0.07%</t>
-  </si>
-  <si>
-    <t>0.09%</t>
-  </si>
-  <si>
-    <t>30.30%</t>
-  </si>
-  <si>
-    <t>1.49%</t>
-  </si>
-  <si>
-    <t>450</t>
-  </si>
-  <si>
-    <t>0.40%</t>
-  </si>
-  <si>
-    <t>641</t>
-  </si>
-  <si>
-    <t>0.44%</t>
-  </si>
-  <si>
-    <t>3.39%</t>
-  </si>
-  <si>
-    <t>0.22%</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>0.05%</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>26.32%</t>
-  </si>
-  <si>
-    <t>1.61%</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>0.03%</t>
-  </si>
-  <si>
-    <t>0.17%</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>2.78%</t>
-  </si>
-  <si>
-    <t>429</t>
-  </si>
-  <si>
-    <t>0.38%</t>
-  </si>
-  <si>
-    <t>674</t>
-  </si>
-  <si>
-    <t>0.46%</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>0.12%</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>0.14%</t>
-  </si>
-  <si>
-    <t>5.08%</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>0.08%</t>
-  </si>
-  <si>
-    <t>0.95%</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>80.00%</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>0.18%</t>
-  </si>
-  <si>
-    <t>0.90%</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>0.19%</t>
-  </si>
-  <si>
-    <t>0.98%</t>
-  </si>
-  <si>
-    <t>22.40%</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>0.04%</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>2.04%</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>0.01%</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>0.02%</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>9.09%</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>0.11%</t>
-  </si>
-  <si>
-    <t>9.49%</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>4.65%</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>629</t>
-  </si>
-  <si>
-    <t>0.55%</t>
-  </si>
-  <si>
-    <t>0.77%</t>
-  </si>
-  <si>
-    <t>968</t>
-  </si>
-  <si>
-    <t>0.66%</t>
-  </si>
-  <si>
-    <t>0.69%</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>0.10%</t>
-  </si>
-  <si>
-    <t>3.13%</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>0.24%</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>0.26%</t>
-  </si>
-  <si>
-    <t>0.25%</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>0.30%</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>6.15%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -585,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -593,6 +302,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,35 +690,35 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>67</v>
+      <c r="D2" s="3">
+        <v>470</v>
       </c>
       <c r="E2">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" t="s">
-        <v>70</v>
+      <c r="F2" s="4">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>636</v>
       </c>
       <c r="I2">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" t="s">
-        <v>74</v>
+      <c r="J2" s="4">
+        <v>4.3E-3</v>
+      </c>
+      <c r="K2" s="4">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1.03E-2</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -1014,17 +726,17 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>74</v>
+      <c r="P2" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
       </c>
       <c r="R2">
         <v>1711.0169491525426</v>
       </c>
-      <c r="S2" t="s">
-        <v>76</v>
+      <c r="S2" s="5">
+        <v>0</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -1043,35 +755,35 @@
       <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
-        <v>77</v>
+      <c r="D3" s="3">
+        <v>67</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" t="s">
-        <v>80</v>
+      <c r="F3" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>105</v>
       </c>
       <c r="I3">
         <v>3</v>
       </c>
-      <c r="J3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M3" t="s">
-        <v>74</v>
+      <c r="J3" s="4">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="K3" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -1079,17 +791,17 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>74</v>
+      <c r="P3" s="4">
+        <v>1.49E-2</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
       </c>
       <c r="R3">
         <v>2075.4237288135596</v>
       </c>
-      <c r="S3" t="s">
-        <v>76</v>
+      <c r="S3" s="5">
+        <v>0</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -1108,35 +820,35 @@
       <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
-        <v>85</v>
+      <c r="D4" s="3">
+        <v>450</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" t="s">
-        <v>87</v>
+      <c r="F4" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4.3E-3</v>
+      </c>
+      <c r="H4" s="3">
+        <v>641</v>
       </c>
       <c r="I4">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
-        <v>88</v>
-      </c>
-      <c r="K4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M4" t="s">
-        <v>74</v>
+      <c r="J4" s="4">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="K4" s="4">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="L4" s="4">
+        <v>3.39E-2</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -1144,17 +856,17 @@
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="P4" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>74</v>
+      <c r="P4" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
       </c>
       <c r="R4">
         <v>1882.2033898305085</v>
       </c>
-      <c r="S4" t="s">
-        <v>76</v>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -1173,35 +885,35 @@
       <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3">
+        <v>62</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
         <v>91</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" t="s">
-        <v>93</v>
-      </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" t="s">
-        <v>94</v>
-      </c>
-      <c r="M5" t="s">
-        <v>74</v>
+      <c r="J5" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.26319999999999999</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -1209,17 +921,17 @@
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>74</v>
+      <c r="P5" s="4">
+        <v>1.61E-2</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
       </c>
       <c r="R5">
         <v>2117.7966101694915</v>
       </c>
-      <c r="S5" t="s">
-        <v>76</v>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -1238,35 +950,35 @@
       <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
-        <v>96</v>
+      <c r="D6" s="3">
+        <v>36</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
-      <c r="F6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" t="s">
-        <v>99</v>
+      <c r="F6" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>45</v>
       </c>
       <c r="I6">
         <v>4</v>
       </c>
-      <c r="J6" t="s">
-        <v>97</v>
-      </c>
-      <c r="K6" t="s">
-        <v>79</v>
-      </c>
-      <c r="L6" t="s">
-        <v>100</v>
-      </c>
-      <c r="M6" t="s">
-        <v>100</v>
+      <c r="J6" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="L6" s="4">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4">
+        <v>1</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1274,17 +986,17 @@
       <c r="O6">
         <v>0</v>
       </c>
-      <c r="P6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>74</v>
+      <c r="P6" s="4">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
       </c>
       <c r="R6">
         <v>1778.8135593220341</v>
       </c>
-      <c r="S6" t="s">
-        <v>76</v>
+      <c r="S6" s="5">
+        <v>0</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -1303,35 +1015,35 @@
       <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
-        <v>102</v>
+      <c r="D7" s="3">
+        <v>429</v>
       </c>
       <c r="E7">
         <v>11</v>
       </c>
-      <c r="F7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" t="s">
-        <v>104</v>
+      <c r="F7" s="4">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>674</v>
       </c>
       <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" t="s">
-        <v>103</v>
-      </c>
-      <c r="L7" t="s">
-        <v>73</v>
-      </c>
-      <c r="M7" t="s">
-        <v>74</v>
+      <c r="J7" s="4">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="K7" s="4">
+        <v>3.8E-3</v>
+      </c>
+      <c r="L7" s="4">
+        <v>1.03E-2</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1339,17 +1051,17 @@
       <c r="O7">
         <v>0</v>
       </c>
-      <c r="P7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>74</v>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
-      <c r="S7" t="s">
-        <v>76</v>
+      <c r="S7" s="5">
+        <v>0</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1368,35 +1080,35 @@
       <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
-        <v>106</v>
+      <c r="D8" s="3">
+        <v>139</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" t="s">
-        <v>108</v>
+      <c r="F8" s="4">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="H8" s="3">
+        <v>200</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
-      <c r="J8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K8" t="s">
-        <v>78</v>
-      </c>
-      <c r="L8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M8" t="s">
-        <v>74</v>
+      <c r="J8" s="4">
+        <v>1.4E-3</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="L8" s="4">
+        <v>5.0799999999999998E-2</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1404,17 +1116,17 @@
       <c r="O8">
         <v>0</v>
       </c>
-      <c r="P8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>74</v>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="S8" t="s">
-        <v>76</v>
+      <c r="S8" s="5">
+        <v>0</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -1433,35 +1145,35 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
-        <v>111</v>
+      <c r="D9" s="3">
+        <v>77</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
-      <c r="F9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s">
-        <v>112</v>
+      <c r="F9" s="4">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>116</v>
       </c>
       <c r="I9">
         <v>7</v>
       </c>
-      <c r="J9" t="s">
-        <v>113</v>
-      </c>
-      <c r="K9" t="s">
-        <v>90</v>
-      </c>
-      <c r="L9" t="s">
-        <v>114</v>
-      </c>
-      <c r="M9" t="s">
-        <v>74</v>
+      <c r="J9" s="4">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="K9" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="L9" s="4">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1469,17 +1181,17 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="P9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>74</v>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
-      <c r="S9" t="s">
-        <v>76</v>
+      <c r="S9" s="5">
+        <v>0</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1498,35 +1210,35 @@
       <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
-        <v>115</v>
+      <c r="D10" s="3">
+        <v>5</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s">
-        <v>115</v>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" t="s">
-        <v>74</v>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1534,17 +1246,17 @@
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="P10" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>74</v>
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
-      <c r="S10" t="s">
-        <v>76</v>
+      <c r="S10" s="5">
+        <v>0</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -1563,35 +1275,35 @@
       <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
-        <v>117</v>
+      <c r="D11" s="3">
+        <v>207</v>
       </c>
       <c r="E11">
         <v>21</v>
       </c>
-      <c r="F11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" t="s">
-        <v>120</v>
+      <c r="F11" s="4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>272</v>
       </c>
       <c r="I11">
         <v>31</v>
       </c>
-      <c r="J11" t="s">
-        <v>121</v>
-      </c>
-      <c r="K11" t="s">
-        <v>122</v>
-      </c>
-      <c r="L11" t="s">
-        <v>123</v>
-      </c>
-      <c r="M11" t="s">
-        <v>74</v>
+      <c r="J11" s="4">
+        <v>1.9E-3</v>
+      </c>
+      <c r="K11" s="4">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.224</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1599,17 +1311,17 @@
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="P11" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>74</v>
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0</v>
       </c>
       <c r="R11">
         <v>0</v>
       </c>
-      <c r="S11" t="s">
-        <v>76</v>
+      <c r="S11" s="5">
+        <v>0</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -1628,35 +1340,35 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="s">
-        <v>124</v>
+      <c r="D12" s="3">
+        <v>40</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" t="s">
-        <v>126</v>
+      <c r="F12" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>64</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" t="s">
-        <v>125</v>
-      </c>
-      <c r="K12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" t="s">
-        <v>127</v>
-      </c>
-      <c r="M12" t="s">
-        <v>74</v>
+      <c r="J12" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1664,17 +1376,17 @@
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>74</v>
+      <c r="P12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
-      <c r="S12" t="s">
-        <v>76</v>
+      <c r="S12" s="5">
+        <v>0</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -1693,35 +1405,35 @@
       <c r="C13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" t="s">
-        <v>128</v>
+      <c r="D13" s="3">
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" t="s">
-        <v>129</v>
-      </c>
-      <c r="G13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" t="s">
-        <v>130</v>
+      <c r="F13" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>16</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" t="s">
-        <v>129</v>
-      </c>
-      <c r="K13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M13" t="s">
-        <v>74</v>
+      <c r="J13" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1729,17 +1441,17 @@
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>74</v>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0</v>
       </c>
       <c r="R13">
         <v>0</v>
       </c>
-      <c r="S13" t="s">
-        <v>76</v>
+      <c r="S13" s="5">
+        <v>0</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -1758,35 +1470,35 @@
       <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" t="s">
-        <v>131</v>
+      <c r="D14" s="3">
+        <v>30</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" t="s">
-        <v>132</v>
+      <c r="F14" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>53</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>125</v>
-      </c>
-      <c r="K14" t="s">
-        <v>97</v>
-      </c>
-      <c r="L14" t="s">
-        <v>74</v>
-      </c>
-      <c r="M14" t="s">
-        <v>74</v>
+      <c r="J14" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="K14" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1794,17 +1506,17 @@
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>74</v>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
       </c>
       <c r="R14">
         <v>0</v>
       </c>
-      <c r="S14" t="s">
-        <v>76</v>
+      <c r="S14" s="5">
+        <v>0</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -1823,35 +1535,35 @@
       <c r="C15" t="s">
         <v>48</v>
       </c>
-      <c r="D15" t="s">
-        <v>133</v>
+      <c r="D15" s="3">
+        <v>28</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" t="s">
-        <v>135</v>
+      <c r="F15" s="4">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>35</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" t="s">
-        <v>136</v>
-      </c>
-      <c r="M15" t="s">
-        <v>74</v>
+      <c r="J15" s="4">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1859,17 +1571,17 @@
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>74</v>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
       </c>
       <c r="R15">
         <v>0</v>
       </c>
-      <c r="S15" t="s">
-        <v>76</v>
+      <c r="S15" s="5">
+        <v>0</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -1888,35 +1600,35 @@
       <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="D16" t="s">
-        <v>137</v>
+      <c r="D16" s="3">
+        <v>106</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" t="s">
-        <v>138</v>
+      <c r="F16" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G16" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="H16" s="3">
+        <v>156</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
-      <c r="J16" t="s">
-        <v>139</v>
-      </c>
-      <c r="K16" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16" t="s">
-        <v>140</v>
-      </c>
-      <c r="M16" t="s">
-        <v>74</v>
+      <c r="J16" s="4">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K16" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9.4899999999999998E-2</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1924,17 +1636,17 @@
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="P16" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>74</v>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
-      <c r="S16" t="s">
-        <v>76</v>
+      <c r="S16" s="5">
+        <v>0</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -1953,35 +1665,35 @@
       <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
-        <v>106</v>
+      <c r="D17" s="3">
+        <v>139</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
-      <c r="F17" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s">
-        <v>141</v>
+      <c r="F17" s="4">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>188</v>
       </c>
       <c r="I17">
         <v>7</v>
       </c>
-      <c r="J17" t="s">
-        <v>79</v>
-      </c>
-      <c r="K17" t="s">
-        <v>90</v>
-      </c>
-      <c r="L17" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" t="s">
-        <v>74</v>
+      <c r="J17" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="K17" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="L17" s="4">
+        <v>4.65E-2</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1989,17 +1701,17 @@
       <c r="O17">
         <v>0</v>
       </c>
-      <c r="P17" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>74</v>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0</v>
       </c>
       <c r="R17">
         <v>0</v>
       </c>
-      <c r="S17" t="s">
-        <v>76</v>
+      <c r="S17" s="5">
+        <v>0</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2018,35 +1730,35 @@
       <c r="C18" t="s">
         <v>54</v>
       </c>
-      <c r="D18" t="s">
-        <v>143</v>
+      <c r="D18" s="3">
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" t="s">
-        <v>143</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" t="s">
-        <v>74</v>
-      </c>
-      <c r="L18" t="s">
-        <v>100</v>
-      </c>
-      <c r="M18" t="s">
-        <v>74</v>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2054,17 +1766,17 @@
       <c r="O18">
         <v>0</v>
       </c>
-      <c r="P18" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>74</v>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0</v>
       </c>
       <c r="R18">
         <v>0</v>
       </c>
-      <c r="S18" t="s">
-        <v>76</v>
+      <c r="S18" s="5">
+        <v>0</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -2083,35 +1795,35 @@
       <c r="C19" t="s">
         <v>56</v>
       </c>
-      <c r="D19" t="s">
-        <v>144</v>
+      <c r="D19" s="3">
+        <v>629</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
-      <c r="F19" t="s">
-        <v>145</v>
-      </c>
-      <c r="G19" t="s">
-        <v>146</v>
-      </c>
-      <c r="H19" t="s">
-        <v>147</v>
+      <c r="F19" s="4">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="G19" s="4">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="H19" s="3">
+        <v>968</v>
       </c>
       <c r="I19">
         <v>22</v>
       </c>
-      <c r="J19" t="s">
-        <v>148</v>
-      </c>
-      <c r="K19" t="s">
-        <v>149</v>
-      </c>
-      <c r="L19" t="s">
-        <v>105</v>
-      </c>
-      <c r="M19" t="s">
-        <v>74</v>
+      <c r="J19" s="4">
+        <v>6.6E-3</v>
+      </c>
+      <c r="K19" s="4">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="L19" s="4">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2119,17 +1831,17 @@
       <c r="O19">
         <v>0</v>
       </c>
-      <c r="P19" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>74</v>
+      <c r="P19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
-      <c r="S19" t="s">
-        <v>76</v>
+      <c r="S19" s="5">
+        <v>0</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -2148,35 +1860,35 @@
       <c r="C20" t="s">
         <v>58</v>
       </c>
-      <c r="D20" t="s">
-        <v>150</v>
+      <c r="D20" s="3">
+        <v>43</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
-      <c r="F20" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" t="s">
-        <v>126</v>
+      <c r="F20" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>64</v>
       </c>
       <c r="I20">
         <v>3</v>
       </c>
-      <c r="J20" t="s">
-        <v>125</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" t="s">
-        <v>74</v>
-      </c>
-      <c r="M20" t="s">
-        <v>74</v>
+      <c r="J20" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="K20" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2184,17 +1896,17 @@
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="P20" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>74</v>
+      <c r="P20" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0</v>
       </c>
       <c r="R20">
         <v>0</v>
       </c>
-      <c r="S20" t="s">
-        <v>76</v>
+      <c r="S20" s="5">
+        <v>0</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2213,35 +1925,35 @@
       <c r="C21" t="s">
         <v>60</v>
       </c>
-      <c r="D21" t="s">
-        <v>151</v>
+      <c r="D21" s="3">
+        <v>2</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" t="s">
-        <v>151</v>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" t="s">
-        <v>74</v>
-      </c>
-      <c r="K21" t="s">
-        <v>74</v>
-      </c>
-      <c r="L21" t="s">
-        <v>100</v>
-      </c>
-      <c r="M21" t="s">
-        <v>74</v>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
+        <v>1</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2249,17 +1961,17 @@
       <c r="O21">
         <v>0</v>
       </c>
-      <c r="P21" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>74</v>
+      <c r="P21" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0</v>
       </c>
       <c r="R21">
         <v>0</v>
       </c>
-      <c r="S21" t="s">
-        <v>76</v>
+      <c r="S21" s="5">
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2278,35 +1990,35 @@
       <c r="C22" t="s">
         <v>62</v>
       </c>
-      <c r="D22" t="s">
-        <v>152</v>
+      <c r="D22" s="3">
+        <v>103</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
-      <c r="F22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" t="s">
-        <v>153</v>
+      <c r="F22" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G22" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="H22" s="3">
+        <v>145</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
-      <c r="J22" t="s">
-        <v>154</v>
-      </c>
-      <c r="K22" t="s">
-        <v>79</v>
-      </c>
-      <c r="L22" t="s">
-        <v>155</v>
-      </c>
-      <c r="M22" t="s">
-        <v>74</v>
+      <c r="J22" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="K22" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="L22" s="4">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="M22" s="4">
+        <v>0</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2314,17 +2026,17 @@
       <c r="O22">
         <v>0</v>
       </c>
-      <c r="P22" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>74</v>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>0</v>
       </c>
       <c r="R22">
         <v>0</v>
       </c>
-      <c r="S22" t="s">
-        <v>76</v>
+      <c r="S22" s="5">
+        <v>0</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -2343,35 +2055,35 @@
       <c r="C23" t="s">
         <v>64</v>
       </c>
-      <c r="D23" t="s">
-        <v>156</v>
+      <c r="D23" s="3">
+        <v>269</v>
       </c>
       <c r="E23">
         <v>5</v>
       </c>
-      <c r="F23" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" t="s">
-        <v>158</v>
+      <c r="F23" s="4">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="H23" s="3">
+        <v>379</v>
       </c>
       <c r="I23">
         <v>8</v>
       </c>
-      <c r="J23" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" t="s">
-        <v>160</v>
-      </c>
-      <c r="L23" t="s">
-        <v>74</v>
-      </c>
-      <c r="M23" t="s">
-        <v>74</v>
+      <c r="J23" s="4">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="K23" s="4">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="L23" s="4">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4">
+        <v>0</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2379,17 +2091,17 @@
       <c r="O23">
         <v>0</v>
       </c>
-      <c r="P23" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>74</v>
+      <c r="P23" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>0</v>
       </c>
       <c r="R23">
         <v>0</v>
       </c>
-      <c r="S23" t="s">
-        <v>76</v>
+      <c r="S23" s="5">
+        <v>0</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -2408,35 +2120,35 @@
       <c r="C24" t="s">
         <v>66</v>
       </c>
-      <c r="D24" t="s">
-        <v>161</v>
+      <c r="D24" s="3">
+        <v>152</v>
       </c>
       <c r="E24">
         <v>7</v>
       </c>
-      <c r="F24" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" t="s">
-        <v>162</v>
-      </c>
-      <c r="H24" t="s">
-        <v>163</v>
+      <c r="F24" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>194</v>
       </c>
       <c r="I24">
         <v>8</v>
       </c>
-      <c r="J24" t="s">
-        <v>79</v>
-      </c>
-      <c r="K24" t="s">
-        <v>160</v>
-      </c>
-      <c r="L24" t="s">
-        <v>164</v>
-      </c>
-      <c r="M24" t="s">
-        <v>74</v>
+      <c r="J24" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="K24" s="4">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="L24" s="4">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="M24" s="4">
+        <v>0</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -2444,17 +2156,17 @@
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="P24" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>74</v>
+      <c r="P24" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>0</v>
       </c>
       <c r="R24">
         <v>0</v>
       </c>
-      <c r="S24" t="s">
-        <v>76</v>
+      <c r="S24" s="5">
+        <v>0</v>
       </c>
       <c r="T24">
         <v>0</v>
